--- a/shared/ajustes_cargo.xlsx
+++ b/shared/ajustes_cargo.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -787,6 +787,171 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MULTA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Condonacion institucional, no es plata real. C-21 (Puesto de Salud Tupac Amaru) figura EXONERADO en registro_cortes.xlsx desde 2026-02 (bien del pueblo, sin vecino que participe). SOLO REGISTRO: el efecto ya lo hizo el AJUSTE del ledger (CLASE=EXONERACION, 09/08/2026) — esta fila es para el backfill del libro_mayor.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>seguimiento_pueblo|LEER_ANTES|C-21-MULTA-condonacion-institucional-20260809</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>EXONERACION</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>MULTA</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>50</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Condonacion institucional, no es plata real. J-6 (Capilla del Pueblo) figura EXONERADO en registro_cortes.xlsx desde 2026-02 (bien del pueblo, sin vecino que participe). SOLO REGISTRO: el efecto ya lo hizo el AJUSTE del ledger (CLASE=EXONERACION, 09/08/2026) — esta fila es para el backfill del libro_mayor.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>seguimiento_pueblo|LEER_ANTES|J-6-MULTA-condonacion-institucional-20260809</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>EXONERACION</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ACUERDOS</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>75</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Condonacion institucional, no es plata real. J-6 (Capilla del Pueblo) figura EXONERADO en registro_cortes.xlsx desde 2026-02 (bien del pueblo, sin vecino que participe). SOLO REGISTRO: el efecto ya lo hizo el AJUSTE del ledger (CLASE=EXONERACION, 09/08/2026) — esta fila es para el backfill del libro_mayor.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>seguimiento_pueblo|LEER_ANTES|J-6-ACUERDOS-condonacion-institucional-20260809</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>EXONERACION</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CORTE_RECONEXION</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>40</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>La secretaria confirma que el corte no corresponde a S-5 (Valerio Porfilio Javier Santiago) -- salio en corte por falta de pago, pero el pago SI existia: Wagner Trujillo (cobrador) lo retuvo en su yape personal de junio y recien lo recupero en efectivo en julio (abonos_rezagados.xlsx, S/71, MES_ANO_APLICA=2026-07). Reclamo confirmado 28/07/2026 (notas_2026-07.xlsx). Corte es agua: no hay ledger, ESTA FILA HACE EL EFECTO en la corrida de 5_cobranza de agosto (julio ya cerrado). Mismo patron que F1-4/V-14. registro_cortes.xlsx actualizado a ESTADO=EXONERADO.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>6_corte/outputs/audit_penalidad.xlsx + abonos_rezagados.xlsx fila S-5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>EXONERACION</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>

--- a/shared/ajustes_cargo.xlsx
+++ b/shared/ajustes_cargo.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -728,7 +728,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Exonerado por la directiva 01/08/2026 (Carmen Ingaruca Julca). SOLO REGISTRO: el efecto ya lo hizo el AJUSTE del ledger — esta fila es para el backfill del libro_mayor.</t>
+          <t>Exonerado por la directiva 01/08/2026 (Carmen Ingaruca Julca). SOLO REGISTRO: pendiente de aplicar después de la reimputación.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -947,6 +947,126 @@
         </is>
       </c>
       <c r="J13" t="inlineStr">
+        <is>
+          <t>EXONERACION</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MULTA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>50</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Se condona la multa de reunión: la secretaria reconoce confusión al anotar la asistencia y lo da por asistido. SOLO REGISTRO: pendiente de aplicar después de la reimputación.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>seguimiento_pueblo|notas_2026-07|C-19-MULTA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>EXONERACION</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>MULTA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>30</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Multa de faena/reunión condonada por indicación directa. SOLO REGISTRO: pendiente de aplicar después de la reimputación.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>seguimiento_pueblo|notas_2026-07|F1-10-MULTA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>EXONERACION</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>MULTA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>12</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Asistió a faena; se condona solo el saldo pendiente de S/12 y se conserva el pago real de S/8. SOLO REGISTRO: pendiente de aplicar después de la reimputación.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>seguimiento_pueblo|notas_2026-07|R-5-MULTA</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>EXONERACION</t>
         </is>
